--- a/prpe-nov.xlsx
+++ b/prpe-nov.xlsx
@@ -22,7 +22,7 @@
     <sheet name="README" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Tracker'!$A$1:$M$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Tracker'!$A$1:$N$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AI ML Topics'!$A$1:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Engineering Topics'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DSA Mistake Log'!$A$1:$O$2</definedName>
@@ -599,22 +599,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -645,46 +646,51 @@
       </c>
       <c r="F1" s="20" t="inlineStr">
         <is>
-          <t>ML/DE Topic</t>
+          <t>HLD Topic</t>
         </is>
       </c>
       <c r="G1" s="20" t="inlineStr">
         <is>
+          <t>LLD Topic</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H1" s="20" t="inlineStr">
-        <is>
-          <t>Time Target</t>
-        </is>
-      </c>
       <c r="I1" s="20" t="inlineStr">
         <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
           <t>Problem Solved</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="K1" s="20" t="inlineStr">
         <is>
           <t>Solved Without Help</t>
         </is>
       </c>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="L1" s="20" t="inlineStr">
         <is>
           <t>Spoke Out Loud</t>
         </is>
       </c>
-      <c r="L1" s="20" t="inlineStr">
+      <c r="M1" s="20" t="inlineStr">
         <is>
           <t>Mistake Logged</t>
         </is>
       </c>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="N1" s="20" t="inlineStr">
         <is>
           <t>Score 0-5</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2026-08-25</t>
@@ -701,31 +707,36 @@
       <c r="D2" s="5" t="inlineStr"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Arrays + hashing</t>
+          <t>Arrays + hashing (warm-up)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>ML: Bias-variance, overfitting basics</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Solve 1 easy/medium array problem + read bias-variance tradeoff</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>60-75 min</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
+          <t>Solve 1 easy/medium to start rhythm</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="44" customHeight="1">
+      <c r="N2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -742,31 +753,36 @@
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Arrays + hashing</t>
+          <t>Two pointers (warm-up)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>DE: SQL window functions</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Solve 1 hash map problem + write 2 window function queries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>60-75 min</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
+          <t>Solve 1 two pointer problem</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="44" customHeight="1">
+      <c r="N3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="50" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -783,31 +799,36 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Two pointers</t>
+          <t>Sliding window (warm-up)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>ML: Supervised learning overview</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Solve 1 two pointer problem + note when to use which model</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>60-75 min</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
+          <t>Solve 1 sliding window problem</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="44" customHeight="1">
+      <c r="N4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="50" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -824,31 +845,36 @@
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Sliding window</t>
+          <t>Binary search (warm-up)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>DE: Data modeling (star schema)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Solve 1 sliding window problem + sketch a star schema</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>60-75 min</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
+          <t>Solve 1 binary search problem</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
       <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="44" customHeight="1">
+      <c r="N5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-08-29</t>
@@ -865,31 +891,36 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Binary search</t>
+          <t>DP: 1D easy (warm-up)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>ML: Evaluation metrics (precision/recall/F1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Solve 1 binary search problem + write when precision vs recall matters</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>60-75 min</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
+          <t>Solve 1 easy DP (climbing stairs / fibonacci style)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="44" customHeight="1">
+      <c r="N6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="50" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-08-30</t>
@@ -906,31 +937,36 @@
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Revision: re-solve weakest</t>
+          <t>Graphs: BFS easy (warm-up)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>DE: ETL vs ELT basics</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Re-solve 1 missed problem + write ETL pipeline steps</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>60 min</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
+          <t>Solve 1 easy graph (flood fill / number of islands)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>45-60 min</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="44" customHeight="1">
+      <c r="N7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -947,31 +983,36 @@
       <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Weekly review</t>
+          <t>Revision: weakest</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Review all notes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Update tracker, mark confidence on ML/DE topics done</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
+          <t>Re-solve 1 mistake; update tracker</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="44" customHeight="1">
+      <c r="N8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>2026-09-01</t>
@@ -988,31 +1029,36 @@
       <c r="D9" s="15" t="inlineStr"/>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Binary search on answer</t>
+          <t>DP: 1D state transition (house robber, decode ways)</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>ML: Deep learning basics (backprop, activations)</t>
+          <t>SD template: requirements → APIs → data model → architecture → deep dive</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>Solve 1 problem + explain backpropagation in own words</t>
+          <t>What is LLD? OOP basics: classes, objects, encapsulation, abstraction</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr"/>
+          <t>Solve 1 DP + learn SD template + read OOP</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>100 min</t>
+        </is>
+      </c>
       <c r="J9" s="15" t="inlineStr"/>
       <c r="K9" s="15" t="inlineStr"/>
       <c r="L9" s="15" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr"/>
-    </row>
-    <row r="10" ht="44" customHeight="1">
+      <c r="N9" s="15" t="inlineStr"/>
+    </row>
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>2026-09-02</t>
@@ -1029,31 +1075,36 @@
       <c r="D10" s="15" t="inlineStr"/>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Trees: recursive DFS</t>
+          <t>DP: 1D subsequence (LIS, coin change, word break)</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>DE: Spark fundamentals (RDD, DataFrame, lazy eval)</t>
+          <t>Capacity estimation: users, QPS, storage math</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>Solve 1 tree DFS problem + write Spark vs Pandas tradeoffs</t>
+          <t>SOLID: Single Responsibility + Open-Closed</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="I10" s="15" t="inlineStr"/>
+          <t>Solve 1 DP + practice estimation + understand SRP/OCP</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>100 min</t>
+        </is>
+      </c>
       <c r="J10" s="15" t="inlineStr"/>
       <c r="K10" s="15" t="inlineStr"/>
       <c r="L10" s="15" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
-    </row>
-    <row r="11" ht="44" customHeight="1">
+      <c r="N10" s="15" t="inlineStr"/>
+    </row>
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -1070,31 +1121,36 @@
       <c r="D11" s="15" t="inlineStr"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Trees: BFS</t>
+          <t>DP: 2D grid (unique paths, min path sum)</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>ML: Transformers &amp; attention mechanism</t>
+          <t>Database: SQL vs NoSQL, indexes, replication</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Solve 1 BFS problem + diagram self-attention step by step</t>
+          <t>SOLID: Liskov + Interface Segregation + Dependency Inversion</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
+          <t>Solve 1 2D DP + note DB tradeoffs + complete SOLID</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
           <t>100 min</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr"/>
       <c r="J11" s="15" t="inlineStr"/>
       <c r="K11" s="15" t="inlineStr"/>
       <c r="L11" s="15" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
-    </row>
-    <row r="12" ht="44" customHeight="1">
+      <c r="N11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -1111,31 +1167,36 @@
       <c r="D12" s="15" t="inlineStr"/>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Trees: BST</t>
+          <t>Graphs: DFS + cycle detection</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>DE: Batch vs streaming (Kafka basics)</t>
+          <t>Caching: read-aside, write-through, TTL, invalidation</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Solve 1 BST problem + note Kafka partitions and consumer groups</t>
+          <t>Design patterns: Strategy pattern (code it)</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="inlineStr"/>
+          <t>2 hrs. Solve 1 graph + diagram cache + code strategy</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
       <c r="J12" s="15" t="inlineStr"/>
       <c r="K12" s="15" t="inlineStr"/>
       <c r="L12" s="15" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
-    </row>
-    <row r="13" ht="44" customHeight="1">
+      <c r="N12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -1152,31 +1213,36 @@
       <c r="D13" s="15" t="inlineStr"/>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Graphs: BFS</t>
+          <t>Graphs: topological sort (course schedule)</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>ML: LLMs (GPT architecture, tokenization)</t>
+          <t>Message queues: async, pub-sub, Kafka basics</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Solve 1 graph BFS problem + explain how GPT generates text</t>
+          <t>Design patterns: Observer pattern (code it)</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>100 min</t>
-        </is>
-      </c>
-      <c r="I13" s="15" t="inlineStr"/>
+          <t>Solve 1 topo sort + note queue use cases + code observer</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
       <c r="J13" s="15" t="inlineStr"/>
       <c r="K13" s="15" t="inlineStr"/>
       <c r="L13" s="15" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
-    </row>
-    <row r="14" ht="44" customHeight="1">
+      <c r="N13" s="15" t="inlineStr"/>
+    </row>
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>2026-09-06</t>
@@ -1193,31 +1259,36 @@
       <c r="D14" s="15" t="inlineStr"/>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Graphs: DFS + visited</t>
+          <t>Graphs: shortest path / BFS on matrix</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>DE: Data warehousing (OLAP, columnar, partitioning)</t>
+          <t>Load balancing + CDN + horizontal scaling</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Solve 1 graph DFS problem + compare OLAP vs OLTP</t>
+          <t>Design patterns: Factory + Builder</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="I14" s="15" t="inlineStr"/>
+          <t>Solve 1 graph + draw scaling + code factory</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
       <c r="J14" s="15" t="inlineStr"/>
       <c r="K14" s="15" t="inlineStr"/>
       <c r="L14" s="15" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
-    </row>
-    <row r="15" ht="44" customHeight="1">
+      <c r="N14" s="15" t="inlineStr"/>
+    </row>
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -1234,31 +1305,36 @@
       <c r="D15" s="15" t="inlineStr"/>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Revision: trees + graphs</t>
+          <t>Revision: DP + Graphs</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Review week 2 ML/DE notes</t>
+          <t>Review: reproduce SD template from memory</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Re-solve 2 mistakes + quiz yourself on concepts</t>
+          <t>Review: SOLID + patterns from memory</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
+          <t>Re-solve 2 hardest + reproduce learnings</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
           <t>90 min</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr"/>
       <c r="J15" s="15" t="inlineStr"/>
       <c r="K15" s="15" t="inlineStr"/>
       <c r="L15" s="15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
-    </row>
-    <row r="16" ht="44" customHeight="1">
+      <c r="N15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -1275,31 +1351,36 @@
       <c r="D16" s="16" t="inlineStr"/>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>Graphs: topological sort</t>
+          <t>DP: knapsack / take-or-skip (subset sum, partition)</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>ML: RAG (embeddings, vector DB, chunking)</t>
+          <t>URL shortener (full design: requirements → scaling)</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>Solve 1 topo sort problem + design a simple RAG pipeline</t>
+          <t>LLD: Parking lot — identify all entities</t>
         </is>
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
+          <t>Solve 1 DP + design URL shortener + list classes</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr"/>
       <c r="J16" s="16" t="inlineStr"/>
       <c r="K16" s="16" t="inlineStr"/>
       <c r="L16" s="16" t="inlineStr"/>
       <c r="M16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="44" customHeight="1">
+      <c r="N16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -1316,31 +1397,36 @@
       <c r="D17" s="16" t="inlineStr"/>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>DP: 1D state transition</t>
+          <t>DP: interval DP / string DP (edit distance, palindrome)</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>DE: Airflow (DAGs, operators, backfill)</t>
+          <t>Rate limiter (token bucket, sliding window, distributed)</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>Solve 1 1D DP problem + sketch a 3-task DAG</t>
+          <t>LLD: Parking lot — responsibilities + interfaces</t>
         </is>
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
+          <t>Solve 1 DP + design rate limiter + assign responsibilities</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr"/>
       <c r="J17" s="16" t="inlineStr"/>
       <c r="K17" s="16" t="inlineStr"/>
       <c r="L17" s="16" t="inlineStr"/>
       <c r="M17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="44" customHeight="1">
+      <c r="N17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -1357,31 +1443,36 @@
       <c r="D18" s="16" t="inlineStr"/>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>DP: 1D subsequence</t>
+          <t>Trees: DFS recursive (diameter, path sum, LCA)</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>ML: Feature engineering + feature stores</t>
+          <t>Consistency: strong vs eventual, CAP theorem</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>Solve 1 DP problem (LIS/coin change) + note feature types</t>
+          <t>LLD: Parking lot — complete flows + edge cases</t>
         </is>
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
+          <t>Solve 1 tree + study consistency + finish parking lot</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr"/>
       <c r="J18" s="16" t="inlineStr"/>
       <c r="K18" s="16" t="inlineStr"/>
       <c r="L18" s="16" t="inlineStr"/>
       <c r="M18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="44" customHeight="1">
+      <c r="N18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -1398,31 +1489,36 @@
       <c r="D19" s="16" t="inlineStr"/>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>DP: 2D grid</t>
+          <t>Trees: BFS (level order, zigzag, right side view)</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>DE: dbt (models, incremental, tests)</t>
+          <t>Sharding: hash vs range, hot keys, rebalancing</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>Solve 1 2D DP problem + explain incremental materialization</t>
+          <t>LLD: Cache (LRU) — entities, eviction interface</t>
         </is>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
+          <t>Solve 1 tree BFS + study sharding + start cache</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr"/>
       <c r="J19" s="16" t="inlineStr"/>
       <c r="K19" s="16" t="inlineStr"/>
       <c r="L19" s="16" t="inlineStr"/>
       <c r="M19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="44" customHeight="1">
+      <c r="N19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="50" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>2026-09-12</t>
@@ -1439,31 +1535,36 @@
       <c r="D20" s="16" t="inlineStr"/>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>DP: knapsack style</t>
+          <t>Trees: BST (validate, kth smallest, iterator)</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>ML: MLOps (drift, monitoring, retraining)</t>
+          <t>API design: REST, pagination, idempotency, versioning</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>Solve 1 take-or-skip problem + write what triggers retraining</t>
+          <t>LLD: Cache (LRU) — HashMap + DLL implementation</t>
         </is>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
+          <t>Solve 1 BST + write API design + complete cache</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr"/>
       <c r="J20" s="16" t="inlineStr"/>
       <c r="K20" s="16" t="inlineStr"/>
       <c r="L20" s="16" t="inlineStr"/>
       <c r="M20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="44" customHeight="1">
+      <c r="N20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21" ht="50" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>2026-09-13</t>
@@ -1480,31 +1581,36 @@
       <c r="D21" s="16" t="inlineStr"/>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>Heap / priority queue</t>
+          <t>Binary search on answer (min days, capacity, koko)</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>DE: File formats (Parquet, Delta Lake, Iceberg)</t>
+          <t>Scaling reads: replicas, fan-out, CQRS</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>Solve 1 heap problem + explain columnar advantage</t>
+          <t>LLD: Splitwise — entities, balances, simplify debts</t>
         </is>
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
+          <t>Solve 1 BS-on-answer + study reads + start splitwise</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr"/>
       <c r="J21" s="16" t="inlineStr"/>
       <c r="K21" s="16" t="inlineStr"/>
       <c r="L21" s="16" t="inlineStr"/>
       <c r="M21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="44" customHeight="1">
+      <c r="N21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>2026-09-14</t>
@@ -1521,31 +1627,36 @@
       <c r="D22" s="16" t="inlineStr"/>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>Revision: DP focus</t>
+          <t>Revision: DP + Trees + BS</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>Review: explain RAG + Spark to yourself</t>
+          <t>Review: URL shortener + rate limiter from scratch</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>Re-solve hardest DP + speak ML/DE explanations out loud</t>
+          <t>Review: parking lot + cache from scratch</t>
         </is>
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>90 min</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr"/>
+          <t>Re-solve hardest + redo designs without notes</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
       <c r="J22" s="16" t="inlineStr"/>
       <c r="K22" s="16" t="inlineStr"/>
       <c r="L22" s="16" t="inlineStr"/>
       <c r="M22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="44" customHeight="1">
+      <c r="N22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23" ht="50" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1562,31 +1673,36 @@
       <c r="D23" s="17" t="inlineStr"/>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>Stack / monotonic stack</t>
+          <t>Sliding window hard (min window substring, longest unique)</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>ML: Fine-tuning (LoRA, QLoRA, when vs RAG)</t>
+          <t>Notification system (push, SMS, email, priorities)</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Solve 1 stack problem + compare fine-tune vs RAG tradeoffs</t>
+          <t>LLD: Splitwise — complete flows, settle-up, groups</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr"/>
+          <t>Solve 1 hard sliding window + design notif + finish splitwise</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>2.5 hrs</t>
+        </is>
+      </c>
       <c r="J23" s="17" t="inlineStr"/>
       <c r="K23" s="17" t="inlineStr"/>
       <c r="L23" s="17" t="inlineStr"/>
       <c r="M23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24" ht="44" customHeight="1">
+      <c r="N23" s="17" t="inlineStr"/>
+    </row>
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>2026-09-16</t>
@@ -1603,31 +1719,36 @@
       <c r="D24" s="17" t="inlineStr"/>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>Intervals</t>
+          <t>Heap: merge K sorted, median stream, top K frequent</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>DE: Data quality (Great Expectations, contracts)</t>
+          <t>News feed (fanout write vs read, ranking, celebrity)</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Solve 1 intervals problem + list 5 data quality checks</t>
+          <t>LLD: Elevator — states, scheduling, direction logic</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr"/>
+          <t>Solve 1 heap + design feed + sketch elevator</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>2.5 hrs</t>
+        </is>
+      </c>
       <c r="J24" s="17" t="inlineStr"/>
       <c r="K24" s="17" t="inlineStr"/>
       <c r="L24" s="17" t="inlineStr"/>
       <c r="M24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25" ht="44" customHeight="1">
+      <c r="N24" s="17" t="inlineStr"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -1644,31 +1765,36 @@
       <c r="D25" s="17" t="inlineStr"/>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Backtracking</t>
+          <t>Stack: monotonic stack (next greater, trapping rain)</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>ML: Embeddings &amp; vector search (ANN, HNSW)</t>
+          <t>Chat system (WebSocket, presence, delivery, storage)</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Solve 1 backtracking problem + explain ANN vs exact search</t>
+          <t>LLD: Elevator — complete with edge cases</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr"/>
+          <t>Solve 1 monotonic stack + design chat + finish elevator</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>2.5 hrs</t>
+        </is>
+      </c>
       <c r="J25" s="17" t="inlineStr"/>
       <c r="K25" s="17" t="inlineStr"/>
       <c r="L25" s="17" t="inlineStr"/>
       <c r="M25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26" ht="44" customHeight="1">
+      <c r="N25" s="17" t="inlineStr"/>
+    </row>
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
           <t>2026-09-18</t>
@@ -1685,31 +1811,36 @@
       <c r="D26" s="17" t="inlineStr"/>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>Greedy</t>
+          <t>Backtracking (word search, N-queens, combinations)</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>DE: CDC (Debezium, log-based), data lake layers</t>
+          <t>File storage (upload, chunking, metadata, sync)</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>Solve 1 greedy problem + explain medallion architecture</t>
+          <t>LLD: Movie ticket booking — seats, concurrency</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr"/>
+          <t>Solve 1 backtracking + design file storage + sketch booking</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>2.5 hrs</t>
+        </is>
+      </c>
       <c r="J26" s="17" t="inlineStr"/>
       <c r="K26" s="17" t="inlineStr"/>
       <c r="L26" s="17" t="inlineStr"/>
       <c r="M26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="44" customHeight="1">
+      <c r="N26" s="17" t="inlineStr"/>
+    </row>
+    <row r="27" ht="50" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
           <t>2026-09-19</t>
@@ -1726,31 +1857,36 @@
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>Linked list</t>
+          <t>Greedy (jump game, task scheduler, meeting rooms)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>ML: ML system design (serving, A/B testing)</t>
+          <t>Failure modes: SPOF, cascading, circuit breaker</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>Solve 1 linked list problem + design model serving pipeline</t>
+          <t>LLD: Booking — payment, timeout, state machine</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
+          <t>Solve 1 greedy + study failures + complete booking</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr"/>
       <c r="J27" s="17" t="inlineStr"/>
       <c r="K27" s="17" t="inlineStr"/>
       <c r="L27" s="17" t="inlineStr"/>
       <c r="M27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28" ht="44" customHeight="1">
+      <c r="N27" s="17" t="inlineStr"/>
+    </row>
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
           <t>2026-09-20</t>
@@ -1767,31 +1903,36 @@
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>Trie + union find</t>
+          <t>Intervals + Linked list</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>DE: Performance (partition pruning, broadcast joins)</t>
+          <t>Observability: logs, metrics, traces, alerts</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>Solve 1 of each + explain predicate pushdown</t>
+          <t>LLD: Vending machine — state pattern, transitions</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
+          <t>Solve 1 each + study observability + sketch vending</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr"/>
       <c r="J28" s="17" t="inlineStr"/>
       <c r="K28" s="17" t="inlineStr"/>
       <c r="L28" s="17" t="inlineStr"/>
       <c r="M28" s="17" t="inlineStr"/>
-    </row>
-    <row r="29" ht="44" customHeight="1">
+      <c r="N28" s="17" t="inlineStr"/>
+    </row>
+    <row r="29" ht="50" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
           <t>2026-09-21</t>
@@ -1808,31 +1949,36 @@
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>Revision: all patterns</t>
+          <t>Revision: all hard patterns</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>ML/DE: pick 3 weakest topics and re-read</t>
+          <t>Review: pick weakest HLD, redo</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>Re-solve 2 DSA mistakes + update ML/DE confidence scores</t>
+          <t>Review: pick weakest LLD, redo</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
+          <t>Re-solve 2 mistakes + redo weakest designs</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr"/>
       <c r="J29" s="17" t="inlineStr"/>
       <c r="K29" s="17" t="inlineStr"/>
       <c r="L29" s="17" t="inlineStr"/>
       <c r="M29" s="17" t="inlineStr"/>
-    </row>
-    <row r="30" ht="44" customHeight="1">
+      <c r="N29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -1849,31 +1995,36 @@
       <c r="D30" s="18" t="inlineStr"/>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>Timed: arrays + hashing + two pointers (50 min)</t>
+          <t>Timed: DP problems (60 min)</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>ML: Explain transformers + RAG out loud</t>
+          <t>Revise URL shortener + rate limiter</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>Solve 2 problems timed + record ML explanation</t>
+          <t>LLD: Snake and ladder — board, dice, players</t>
         </is>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
+          <t>Solve 2 DP timed + speak HLD + sketch game</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I30" s="18" t="inlineStr"/>
       <c r="J30" s="18" t="inlineStr"/>
       <c r="K30" s="18" t="inlineStr"/>
       <c r="L30" s="18" t="inlineStr"/>
       <c r="M30" s="18" t="inlineStr"/>
-    </row>
-    <row r="31" ht="44" customHeight="1">
+      <c r="N30" s="18" t="inlineStr"/>
+    </row>
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
           <t>2026-09-23</t>
@@ -1890,31 +2041,36 @@
       <c r="D31" s="18" t="inlineStr"/>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>Timed: trees + graphs (50 min)</t>
+          <t>Timed: Graphs + Trees (50 min)</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>DE: Explain Spark shuffle + Kafka ordering out loud</t>
+          <t>Revise notification + news feed</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>Solve 2 problems timed + record DE explanation</t>
+          <t>LLD: Snake and ladder — complete with rules</t>
         </is>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
+          <t>Solve 2 timed + speak HLD + finish game</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I31" s="18" t="inlineStr"/>
       <c r="J31" s="18" t="inlineStr"/>
       <c r="K31" s="18" t="inlineStr"/>
       <c r="L31" s="18" t="inlineStr"/>
       <c r="M31" s="18" t="inlineStr"/>
-    </row>
-    <row r="32" ht="44" customHeight="1">
+      <c r="N31" s="18" t="inlineStr"/>
+    </row>
+    <row r="32" ht="50" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -1931,31 +2087,36 @@
       <c r="D32" s="18" t="inlineStr"/>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>Timed: DP + heap (60 min)</t>
+          <t>Timed: Binary search + Sliding window (50 min)</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>ML: Practice ML system design question</t>
+          <t>Revise chat + file storage</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>Solve 2 problems timed + design recommendation system</t>
+          <t>LLD: Logger framework — levels, sinks, format</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
         <is>
-          <t>3 hrs</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr"/>
+          <t>Solve 2 timed + speak HLD + sketch logger</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="inlineStr">
+        <is>
+          <t>2.5 hrs</t>
+        </is>
+      </c>
       <c r="J32" s="18" t="inlineStr"/>
       <c r="K32" s="18" t="inlineStr"/>
       <c r="L32" s="18" t="inlineStr"/>
       <c r="M32" s="18" t="inlineStr"/>
-    </row>
-    <row r="33" ht="44" customHeight="1">
+      <c r="N32" s="18" t="inlineStr"/>
+    </row>
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
         <is>
           <t>2026-09-25</t>
@@ -1972,31 +2133,36 @@
       <c r="D33" s="18" t="inlineStr"/>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>Timed: mixed medium (50 min)</t>
+          <t>Timed: Heap + Stack + mixed (50 min)</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>DE: Practice DE system design question</t>
+          <t>Revise consistency, sharding, failure, observability</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>Solve 2 problems timed + design real-time analytics pipeline</t>
+          <t>LLD: Logger — complete with interface and extension</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>3 hrs</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr"/>
+          <t>Solve 2 timed + review concepts + finish logger</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>2.5 hrs</t>
+        </is>
+      </c>
       <c r="J33" s="18" t="inlineStr"/>
       <c r="K33" s="18" t="inlineStr"/>
       <c r="L33" s="18" t="inlineStr"/>
       <c r="M33" s="18" t="inlineStr"/>
-    </row>
-    <row r="34" ht="44" customHeight="1">
+      <c r="N33" s="18" t="inlineStr"/>
+    </row>
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
           <t>2026-09-26</t>
@@ -2013,31 +2179,36 @@
       <c r="D34" s="18" t="inlineStr"/>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>Mistake repair: top 5 DSA</t>
+          <t>Mistake repair: top 5 hardest DSA</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>ML/DE: review all "Not started" topics</t>
+          <t>Review all HLD tradeoffs</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>Re-solve DSA mistakes + study remaining gaps</t>
+          <t>Review all LLD: reproduce from memory</t>
         </is>
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
+          <t>Re-solve hardest mistakes + tighten designs</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I34" s="18" t="inlineStr"/>
       <c r="J34" s="18" t="inlineStr"/>
       <c r="K34" s="18" t="inlineStr"/>
       <c r="L34" s="18" t="inlineStr"/>
       <c r="M34" s="18" t="inlineStr"/>
-    </row>
-    <row r="35" ht="44" customHeight="1">
+      <c r="N34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35" ht="50" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
           <t>2026-09-27</t>
@@ -2059,26 +2230,31 @@
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>Mock: explain one ML + one DE topic cold</t>
+          <t>Practice explaining 1 HLD cold</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t>Re-solve + practice cold explanations</t>
+          <t>Practice explaining 1 LLD cold</t>
         </is>
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
+          <t>Re-solve + cold explanations</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr"/>
       <c r="J35" s="18" t="inlineStr"/>
       <c r="K35" s="18" t="inlineStr"/>
       <c r="L35" s="18" t="inlineStr"/>
       <c r="M35" s="18" t="inlineStr"/>
-    </row>
-    <row r="36" ht="44" customHeight="1">
+      <c r="N35" s="18" t="inlineStr"/>
+    </row>
+    <row r="36" ht="50" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -2095,31 +2271,36 @@
       <c r="D36" s="18" t="inlineStr"/>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>Revision: weakest timed block</t>
+          <t>Trie + Union find (if not covered)</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>Full concept review</t>
+          <t>Weakest HLD from scratch</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
-          <t>Do 1 weak-area problem + quiz all ML/DE concepts</t>
+          <t>Weakest LLD from scratch</t>
         </is>
       </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
+          <t>Cover remaining + redo weakest</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr"/>
       <c r="J36" s="18" t="inlineStr"/>
       <c r="K36" s="18" t="inlineStr"/>
       <c r="L36" s="18" t="inlineStr"/>
       <c r="M36" s="18" t="inlineStr"/>
-    </row>
-    <row r="37" ht="44" customHeight="1">
+      <c r="N36" s="18" t="inlineStr"/>
+    </row>
+    <row r="37" ht="50" customHeight="1">
       <c r="A37" s="19" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2136,31 +2317,36 @@
       <c r="D37" s="19" t="inlineStr"/>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>Final: arrays + hashing + sliding window</t>
+          <t>Final: DP 1D + 2D + knapsack</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>ML: Revise critical topics (transformers, LLMs, RAG)</t>
+          <t>Revise: URL shortener + rate limiter</t>
         </is>
       </c>
       <c r="G37" s="19" t="inlineStr">
         <is>
-          <t>Re-solve 2 DSA + speak ML answers out loud</t>
+          <t>Revise: parking lot + cache LRU</t>
         </is>
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
+          <t>Re-solve 2 hardest DP + speak designs</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr"/>
       <c r="J37" s="19" t="inlineStr"/>
       <c r="K37" s="19" t="inlineStr"/>
       <c r="L37" s="19" t="inlineStr"/>
       <c r="M37" s="19" t="inlineStr"/>
-    </row>
-    <row r="38" ht="44" customHeight="1">
+      <c r="N37" s="19" t="inlineStr"/>
+    </row>
+    <row r="38" ht="50" customHeight="1">
       <c r="A38" s="19" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2177,31 +2363,36 @@
       <c r="D38" s="19" t="inlineStr"/>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>Final: binary search + trees</t>
+          <t>Final: Graphs + topo sort + shortest path</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>DE: Revise critical topics (SQL, Spark, modeling)</t>
+          <t>Revise: notifications + news feed</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>Re-solve 2 DSA + speak DE answers out loud</t>
+          <t>Revise: splitwise + elevator</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
+          <t>Re-solve 2 graph + speak designs</t>
+        </is>
+      </c>
+      <c r="I38" s="19" t="inlineStr">
+        <is>
           <t>2.5 hrs</t>
         </is>
       </c>
-      <c r="I38" s="19" t="inlineStr"/>
       <c r="J38" s="19" t="inlineStr"/>
       <c r="K38" s="19" t="inlineStr"/>
       <c r="L38" s="19" t="inlineStr"/>
       <c r="M38" s="19" t="inlineStr"/>
-    </row>
-    <row r="39" ht="44" customHeight="1">
+      <c r="N38" s="19" t="inlineStr"/>
+    </row>
+    <row r="39" ht="50" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
         <is>
           <t>2026-10-01</t>
@@ -2218,31 +2409,36 @@
       <c r="D39" s="19" t="inlineStr"/>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>Final: graphs + topo sort</t>
+          <t>Final: Trees + BST + binary search</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>ML: Revise high topics (MLOps, embeddings, reco)</t>
+          <t>Revise: chat + file storage</t>
         </is>
       </c>
       <c r="G39" s="19" t="inlineStr">
         <is>
-          <t>Re-solve 2 DSA + write concise ML answers</t>
+          <t>Revise: booking + vending machine</t>
         </is>
       </c>
       <c r="H39" s="19" t="inlineStr">
         <is>
+          <t>Re-solve 2 tree/BS + speak designs</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr"/>
       <c r="J39" s="19" t="inlineStr"/>
       <c r="K39" s="19" t="inlineStr"/>
       <c r="L39" s="19" t="inlineStr"/>
       <c r="M39" s="19" t="inlineStr"/>
-    </row>
-    <row r="40" ht="44" customHeight="1">
+      <c r="N39" s="19" t="inlineStr"/>
+    </row>
+    <row r="40" ht="50" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
           <t>2026-10-02</t>
@@ -2259,31 +2455,36 @@
       <c r="D40" s="19" t="inlineStr"/>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>Final: DP 1D + 2D</t>
+          <t>Final: Sliding window + heap + stack</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>DE: Revise high topics (Kafka, Airflow, dbt, quality)</t>
+          <t>Revise: scaling, caching, consistency, failure</t>
         </is>
       </c>
       <c r="G40" s="19" t="inlineStr">
         <is>
-          <t>Re-solve 2 DP + write concise DE answers</t>
+          <t>Revise: snake &amp; ladder + logger</t>
         </is>
       </c>
       <c r="H40" s="19" t="inlineStr">
         <is>
+          <t>Re-solve 2 + review all concepts</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr"/>
       <c r="J40" s="19" t="inlineStr"/>
       <c r="K40" s="19" t="inlineStr"/>
       <c r="L40" s="19" t="inlineStr"/>
       <c r="M40" s="19" t="inlineStr"/>
-    </row>
-    <row r="41" ht="44" customHeight="1">
+      <c r="N40" s="19" t="inlineStr"/>
+    </row>
+    <row r="41" ht="50" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
           <t>2026-10-03</t>
@@ -2300,31 +2501,36 @@
       <c r="D41" s="19" t="inlineStr"/>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>Final: heap + stack + intervals</t>
+          <t>Final: Backtracking + greedy + intervals</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>ML/DE: Final weak-topic pass</t>
+          <t>Behavioral: ownership, failure, impact, conflict</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
         <is>
-          <t>Re-solve 2 DSA + address final confidence gaps</t>
+          <t>Revise: SOLID + all design patterns</t>
         </is>
       </c>
       <c r="H41" s="19" t="inlineStr">
         <is>
+          <t>Re-solve 2 + practice behavioral + review SOLID</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
           <t>2 hrs</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr"/>
       <c r="J41" s="19" t="inlineStr"/>
       <c r="K41" s="19" t="inlineStr"/>
       <c r="L41" s="19" t="inlineStr"/>
       <c r="M41" s="19" t="inlineStr"/>
-    </row>
-    <row r="42" ht="44" customHeight="1">
+      <c r="N41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42" ht="50" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
           <t>2026-10-04</t>
@@ -2341,31 +2547,36 @@
       <c r="D42" s="19" t="inlineStr"/>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>Final simulation</t>
+          <t>Final: full practice day</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>Full mock: DSA + ML/DE depth + behavioral</t>
+          <t>Reproduce any HLD from scratch (45 min)</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>Simulate full interview day: 2 DSA + 1 depth + 1 behavioral</t>
+          <t>Reproduce any LLD from scratch (40 min)</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
+          <t>Full: 2 DSA + 1 HLD + 1 LLD from scratch</t>
+        </is>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
+        <is>
           <t>3 hrs</t>
         </is>
       </c>
-      <c r="I42" s="19" t="inlineStr"/>
       <c r="J42" s="19" t="inlineStr"/>
       <c r="K42" s="19" t="inlineStr"/>
       <c r="L42" s="19" t="inlineStr"/>
       <c r="M42" s="19" t="inlineStr"/>
-    </row>
-    <row r="43" ht="44" customHeight="1">
+      <c r="N42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43" ht="50" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2387,41 +2598,46 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>Read all notes one last time</t>
+          <t>Read HLD notes only</t>
         </is>
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>No new problems. Trust your prep. Sleep well.</t>
+          <t>Read LLD notes only</t>
         </is>
       </c>
       <c r="H43" s="19" t="inlineStr">
         <is>
+          <t>No new problems. Trust prep. Rest.</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
           <t>1 hr</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr"/>
       <c r="J43" s="19" t="inlineStr"/>
       <c r="K43" s="19" t="inlineStr"/>
       <c r="L43" s="19" t="inlineStr"/>
       <c r="M43" s="19" t="inlineStr"/>
+      <c r="N43" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M43"/>
+  <autoFilter ref="A1:N43"/>
   <dataValidations count="5">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,Partial"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2849,7 +3065,7 @@
         </is>
       </c>
       <c r="B2" s="8">
-        <f>COUNTIF('Daily Tracker'!M2:M200,"&gt;0")</f>
+        <f>COUNTIF('Daily Tracker'!N2:N200,"&gt;0")</f>
         <v/>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -2870,7 +3086,7 @@
         </is>
       </c>
       <c r="B3" s="8">
-        <f>IFERROR(AVERAGEIF('Daily Tracker'!M2:M200,"&gt;0"),"")</f>
+        <f>IFERROR(AVERAGEIF('Daily Tracker'!N2:N200,"&gt;0"),"")</f>
         <v/>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -3080,7 +3296,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Combined interview tracker for Senior SWE preparing DSA + AI/ML + Data Engineering. Daily Tracker shows exactly what to do each day across all areas. AI ML Topics and Data Engineering Topics sheets are reference + confidence tracking. 6 weeks from start date, building from light habit to full simulation.</t>
+          <t>Senior SDE interview tracker. Daily Tracker focuses on DSA + SDE depth (system design, backend, LLD). AI ML Topics and Data Engineering Topics sheets are for your ML/AI prep at your own pace — not forced daily. 6 weeks from 2026-08-25, building from light habit to full simulation.</t>
         </is>
       </c>
     </row>
@@ -3313,27 +3529,27 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Build habit</t>
+          <t>Lenient — build rhythm</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Light DSA (arrays, hash, 2ptr, sliding, binary search) + intro ML/DE concepts</t>
+          <t>Warm-up: arrays, 2ptr, sliding, BS + easy DP + easy graph | No HLD/LLD</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>60-75 min</t>
+          <t>45-60 min</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Show up daily; one DSA + one concept note</t>
+          <t>Just show up daily and solve one</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>5+ days done, habit forming</t>
+          <t>5+ days done; can solve easy/medium</t>
         </is>
       </c>
     </row>
@@ -3345,27 +3561,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>DSA rhythm + deeper concepts</t>
+          <t>Hard DSA first + HLD/LLD basics</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>Trees, graphs, BST + DL basics, transformers, Spark, Kafka, warehousing</t>
+          <t>DP 1D/2D + Graphs (DFS, topo, BFS) + SD template, estimation, cache, DB + OOP, SOLID, patterns</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>90-120 min</t>
+          <t>100 min - 2 hrs</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>One problem + one depth topic daily</t>
+          <t>One hard DSA + one HLD + one LLD concept</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Trees/graphs no longer scary; ML/DE vocabulary built</t>
+          <t>DP/Graph not terrifying; SD template + SOLID memorized</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3593,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Critical patterns + production ML/DE</t>
+          <t>More hard DSA + first full designs</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DP (1D, 2D, knapsack), heap, stack + RAG, Airflow, dbt, feature eng, MLOps</t>
+          <t>DP knapsack/string, Trees, BST, BS-on-answer + URL shortener, rate limiter + Parking lot, Cache LRU, Splitwise</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3392,12 +3608,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>DP state definitions + production concepts</t>
+          <t>Hard DSA + complete designs</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>DP approachable; can explain RAG and Spark</t>
+          <t>2 HLD and 3 LLD done from scratch</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3625,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Remaining patterns + system thinking</t>
+          <t>Remaining hard + deeper designs</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Intervals, backtracking, greedy, trie + fine-tuning, CDC, ML serving, data quality</t>
+          <t>Sliding window hard, heap, monotonic stack, backtracking, greedy + feed, chat, file storage + elevator, booking, vending machine</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3424,12 +3640,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>All patterns once + system-level ML/DE understanding</t>
+          <t>All hard patterns + all designs</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Full pattern coverage; can discuss tradeoffs</t>
+          <t>Full coverage DSA + HLD + LLD</t>
         </is>
       </c>
     </row>
@@ -3441,27 +3657,27 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Timed practice + integration</t>
+          <t>Timed hard DSA + strengthen designs</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Mixed timed DSA + practice explaining ML/DE concepts cold + mock designs</t>
+          <t>Timed DP/graphs/trees first + revise all HLD + snake &amp; ladder, logger</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>2.5-3 hrs</t>
+          <t>2.5 hrs</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Timer on; speak before code; explain concepts out loud</t>
+          <t>Timed hard problems + reproduce designs from memory</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Can solve under pressure; can explain depth topics</t>
+          <t>Fast under pressure; designs reproducible</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3689,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Final revision + simulation</t>
+          <t>Final revision (hard → easy order)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Re-solve by frequency; final ML/DE pass; full mock simulation; rest</t>
+          <t>DP → Graphs → Trees → BS → rest + reproduce all HLD/LLD + behavioral</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -3488,12 +3704,12 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>No new topics; trust prep; revise and rest</t>
+          <t>No new topics; hard patterns first in revision</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Ready for interview; confident on core areas</t>
+          <t>Ready for Senior SDE interview</t>
         </is>
       </c>
     </row>
@@ -5380,11 +5596,11 @@
         </is>
       </c>
       <c r="C2" s="7">
-        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=1)*('Daily Tracker'!M2:M200))</f>
+        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=1)*('Daily Tracker'!N2:N200))</f>
         <v/>
       </c>
       <c r="D2" s="7">
-        <f>COUNTIFS('Daily Tracker'!B2:B200,1,'Daily Tracker'!I2:I200,"&lt;&gt;")</f>
+        <f>COUNTIFS('Daily Tracker'!B2:B200,1,'Daily Tracker'!J2:J200,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -5409,11 +5625,11 @@
         </is>
       </c>
       <c r="C3" s="7">
-        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=2)*('Daily Tracker'!M2:M200))</f>
+        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=2)*('Daily Tracker'!N2:N200))</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>COUNTIFS('Daily Tracker'!B2:B200,2,'Daily Tracker'!I2:I200,"&lt;&gt;")</f>
+        <f>COUNTIFS('Daily Tracker'!B2:B200,2,'Daily Tracker'!J2:J200,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -5438,11 +5654,11 @@
         </is>
       </c>
       <c r="C4" s="7">
-        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=3)*('Daily Tracker'!M2:M200))</f>
+        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=3)*('Daily Tracker'!N2:N200))</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>COUNTIFS('Daily Tracker'!B2:B200,3,'Daily Tracker'!I2:I200,"&lt;&gt;")</f>
+        <f>COUNTIFS('Daily Tracker'!B2:B200,3,'Daily Tracker'!J2:J200,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -5467,11 +5683,11 @@
         </is>
       </c>
       <c r="C5" s="7">
-        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=4)*('Daily Tracker'!M2:M200))</f>
+        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=4)*('Daily Tracker'!N2:N200))</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS('Daily Tracker'!B2:B200,4,'Daily Tracker'!I2:I200,"&lt;&gt;")</f>
+        <f>COUNTIFS('Daily Tracker'!B2:B200,4,'Daily Tracker'!J2:J200,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
@@ -5496,11 +5712,11 @@
         </is>
       </c>
       <c r="C6" s="7">
-        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=5)*('Daily Tracker'!M2:M200))</f>
+        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=5)*('Daily Tracker'!N2:N200))</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS('Daily Tracker'!B2:B200,5,'Daily Tracker'!I2:I200,"&lt;&gt;")</f>
+        <f>COUNTIFS('Daily Tracker'!B2:B200,5,'Daily Tracker'!J2:J200,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -5525,11 +5741,11 @@
         </is>
       </c>
       <c r="C7" s="7">
-        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=6)*('Daily Tracker'!M2:M200))</f>
+        <f>SUMPRODUCT(('Daily Tracker'!B2:B200=6)*('Daily Tracker'!N2:N200))</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS('Daily Tracker'!B2:B200,6,'Daily Tracker'!I2:I200,"&lt;&gt;")</f>
+        <f>COUNTIFS('Daily Tracker'!B2:B200,6,'Daily Tracker'!J2:J200,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
